--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
@@ -33,7 +33,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 09:28</t>
+    <t xml:space="preserve">2026-09-16 18:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
@@ -6,67 +6,120 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Histórico" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Region" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regiones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Evolucion" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Histórico'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Evolucion'!$A$1:$C$97</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t xml:space="preserve">region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">movilidad_interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lugar_de_mayor_a_menor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metropolitana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29 14:08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plot_migracion_movinterna_2024_metropolitana.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movilidad interna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region de Metropolitana</t>
+  </si>
   <si>
     <t xml:space="preserve">Año</t>
   </si>
   <si>
-    <t xml:space="preserve">Tasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Campo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de creación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16 18:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fuente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIT - MDSF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imagen asociada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plot_migracion_movinterna_2024_metropolitana.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indicador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tasa global de movilidad interna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidad territorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metropolitana (Regional)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024</t>
   </si>
   <si>
-    <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Índice Bruto de Migración (CMI), por 1.000 habitantes</t>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Ríos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarapacá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magallanes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antofagasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Araucanía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arica y Parinacota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Lagos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biobío</t>
   </si>
 </sst>
 </file>
@@ -431,8 +484,10 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="15.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="24.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,57 +497,29 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>2019</v>
+      <c r="A2" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>3.55</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>5.46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>4.53</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>4.53</v>
+      <c r="C2" s="2" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
+  <autoFilter ref="A1:D2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -509,70 +536,1298 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>89.68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>88.24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>80.58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>79.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>73.71</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>73.63</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>71.77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>65.08</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>64.64</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>62.69</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>59.45</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>47.82</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45.29</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B17"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="20.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="19.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>66.53</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>44.57</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>65.39</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>64.41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>31.37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>63.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>57.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>76.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>60.52</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>61.81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>51.14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>46.03</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>48.96</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>44.43</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>40.69</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>50.28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>63.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>47.38</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>64.17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>65.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>35.53</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>70.33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>57.25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>75.47</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>63.22</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>62.51</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>54.86</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>55.86</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>49.06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>40.67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>53.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>79.29</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>65.51</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>82.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>85.43</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>53.85</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>93.87</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>68.91</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>102.05</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>80.56</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>79.64</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>72.9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>73.19</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>79.87</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>69.18</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>56.91</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>73.26</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>79.86</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>64.25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>90.57</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>81.21</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>54.59</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>92.25</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>66.56</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>81.57</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>75.63</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>73.72</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>68.63</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>67.78</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>78.56</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>68.88</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>54.07</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>72.09</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>80.32</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>58.06</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>86.23</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>75.41</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>45.29</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>87.21</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>65.24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>79.32</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>71.77</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>71.89</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>64.66</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>65.09</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>70.49</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>62.6</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>47.19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>65.89</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>80.58</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>59.45</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v>89.68</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>79.45</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>45.29</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>88.24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>64.64</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>78.5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>73.71</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>73.63</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>65.08</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>71.77</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>62.69</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>47.82</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>65.7</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C97"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:08</t>
+    <t xml:space="preserve">2026-09-29 19:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 19:05</t>
+    <t xml:space="preserve">2026-10-01 19:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_movinterna_2024_metropolitana.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:21</t>
+    <t xml:space="preserve">2026-10-05 04:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
